--- a/crimenMeridaNOV2024.xlsx
+++ b/crimenMeridaNOV2024.xlsx
@@ -84,7 +84,7 @@
     <t>c005</t>
   </si>
   <si>
-    <t xml:space="preserve">homicidio </t>
+    <t>homicidio</t>
   </si>
   <si>
     <t xml:space="preserve">los sausales</t>
@@ -269,9 +269,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.000000"/>
       <name val="Arial"/>
@@ -281,13 +281,25 @@
       <sz val="10.000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10.000000"/>
+      <color theme="0" tint="0"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0"/>
+        <bgColor theme="1" tint="0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -317,16 +329,12 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
@@ -812,7 +820,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="7.57421875"/>
-    <col customWidth="1" min="2" max="2" style="1" width="8.8515625"/>
+    <col customWidth="1" min="2" max="2" style="1" width="11.421875"/>
     <col customWidth="1" min="3" max="3" width="25.28125"/>
     <col customWidth="1" min="4" max="4" width="20.28125"/>
     <col customWidth="1" min="5" max="5" width="14.421875"/>
@@ -822,11 +830,11 @@
     <col customWidth="1" min="9" max="257" width="11.5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.75" customHeight="1">
+    <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -852,7 +860,7 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="1">
         <v>45597</v>
       </c>
       <c r="C2" t="s">
@@ -867,10 +875,10 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="3">
         <v>1</v>
       </c>
     </row>
@@ -878,7 +886,7 @@
       <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="1">
         <v>45598</v>
       </c>
       <c r="C3" t="s">
@@ -893,10 +901,10 @@
       <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -904,7 +912,7 @@
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="1">
         <v>45599</v>
       </c>
       <c r="C4" t="s">
@@ -919,10 +927,10 @@
       <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -930,7 +938,7 @@
       <c r="A5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="1">
         <v>45600</v>
       </c>
       <c r="C5" t="s">
@@ -945,10 +953,10 @@
       <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -956,7 +964,7 @@
       <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="1">
         <v>45601</v>
       </c>
       <c r="C6" t="s">
@@ -971,10 +979,10 @@
       <c r="F6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="3">
         <v>1</v>
       </c>
     </row>
@@ -982,7 +990,7 @@
       <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="1">
         <v>45602</v>
       </c>
       <c r="C7" t="s">
@@ -997,10 +1005,10 @@
       <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1008,7 +1016,7 @@
       <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="1">
         <v>45603</v>
       </c>
       <c r="C8" t="s">
@@ -1023,10 +1031,10 @@
       <c r="F8" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1034,7 +1042,7 @@
       <c r="A9" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="1">
         <v>45604</v>
       </c>
       <c r="C9" t="s">
@@ -1049,10 +1057,10 @@
       <c r="F9" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1060,7 +1068,7 @@
       <c r="A10" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="1">
         <v>45605</v>
       </c>
       <c r="C10" t="s">
@@ -1075,10 +1083,10 @@
       <c r="F10" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1086,7 +1094,7 @@
       <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="1">
         <v>45606</v>
       </c>
       <c r="C11" t="s">
@@ -1101,10 +1109,10 @@
       <c r="F11" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1112,7 +1120,7 @@
       <c r="A12" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="1">
         <v>45607</v>
       </c>
       <c r="C12" t="s">
@@ -1127,10 +1135,10 @@
       <c r="F12" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1138,7 +1146,7 @@
       <c r="A13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="1">
         <v>45608</v>
       </c>
       <c r="C13" t="s">
@@ -1153,10 +1161,10 @@
       <c r="F13" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1164,7 +1172,7 @@
       <c r="A14" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="1">
         <v>45609</v>
       </c>
       <c r="C14" t="s">
@@ -1179,10 +1187,10 @@
       <c r="F14" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1190,7 +1198,7 @@
       <c r="A15" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="1">
         <v>45610</v>
       </c>
       <c r="C15" t="s">
@@ -1205,10 +1213,10 @@
       <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1216,7 +1224,7 @@
       <c r="A16" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="1">
         <v>45611</v>
       </c>
       <c r="C16" t="s">
@@ -1228,13 +1236,13 @@
       <c r="E16" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1242,7 +1250,7 @@
       <c r="A17" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="1">
         <v>45612</v>
       </c>
       <c r="C17" t="s">
@@ -1257,10 +1265,10 @@
       <c r="F17" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1268,7 +1276,7 @@
       <c r="A18" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="1">
         <v>45613</v>
       </c>
       <c r="C18" t="s">
@@ -1283,10 +1291,10 @@
       <c r="F18" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1294,7 +1302,7 @@
       <c r="A19" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="1">
         <v>45614</v>
       </c>
       <c r="C19" t="s">
@@ -1309,10 +1317,10 @@
       <c r="F19" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1320,7 +1328,7 @@
       <c r="A20" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="1">
         <v>45615</v>
       </c>
       <c r="C20" t="s">
@@ -1335,10 +1343,10 @@
       <c r="F20" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1346,7 +1354,7 @@
       <c r="A21" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="1">
         <v>45616</v>
       </c>
       <c r="C21" t="s">
@@ -1361,10 +1369,10 @@
       <c r="F21" t="s">
         <v>33</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1372,7 +1380,7 @@
       <c r="A22" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="1">
         <v>45617</v>
       </c>
       <c r="C22" t="s">
@@ -1387,10 +1395,10 @@
       <c r="F22" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1398,7 +1406,7 @@
       <c r="A23" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="1">
         <v>45618</v>
       </c>
       <c r="C23" t="s">
@@ -1413,10 +1421,10 @@
       <c r="F23" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1424,7 +1432,7 @@
       <c r="A24" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="1">
         <v>45619</v>
       </c>
       <c r="C24" t="s">
@@ -1439,10 +1447,10 @@
       <c r="F24" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1450,7 +1458,7 @@
       <c r="A25" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="1">
         <v>45620</v>
       </c>
       <c r="C25" t="s">
@@ -1465,10 +1473,10 @@
       <c r="F25" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1476,7 +1484,7 @@
       <c r="A26" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="1">
         <v>45621</v>
       </c>
       <c r="C26" t="s">
@@ -1491,10 +1499,10 @@
       <c r="F26" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1502,7 +1510,7 @@
       <c r="A27" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="4">
+      <c r="B27" s="1">
         <v>45622</v>
       </c>
       <c r="C27" t="s">
@@ -1517,10 +1525,10 @@
       <c r="F27" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1528,7 +1536,7 @@
       <c r="A28" t="s">
         <v>67</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="1">
         <v>45623</v>
       </c>
       <c r="C28" t="s">
@@ -1543,10 +1551,10 @@
       <c r="F28" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1554,7 +1562,7 @@
       <c r="A29" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="1">
         <v>45624</v>
       </c>
       <c r="C29" t="s">
@@ -1569,10 +1577,10 @@
       <c r="F29" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1580,7 +1588,7 @@
       <c r="A30" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="1">
         <v>45625</v>
       </c>
       <c r="C30" t="s">
@@ -1595,10 +1603,10 @@
       <c r="F30" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1606,7 +1614,7 @@
       <c r="A31" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="4">
+      <c r="B31" s="1">
         <v>45626</v>
       </c>
       <c r="C31" t="s">
@@ -1621,10 +1629,10 @@
       <c r="F31" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1632,7 +1640,7 @@
       <c r="A32" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="4">
+      <c r="B32" s="1">
         <v>45627</v>
       </c>
       <c r="C32" t="s">
@@ -1647,10 +1655,10 @@
       <c r="F32" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1658,7 +1666,7 @@
       <c r="A33" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="4">
+      <c r="B33" s="1">
         <v>45628</v>
       </c>
       <c r="C33" t="s">
@@ -1673,10 +1681,10 @@
       <c r="F33" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1684,7 +1692,7 @@
       <c r="A34" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="4">
+      <c r="B34" s="1">
         <v>45629</v>
       </c>
       <c r="C34" t="s">
@@ -1699,10 +1707,10 @@
       <c r="F34" t="s">
         <v>12</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1710,7 +1718,7 @@
       <c r="A35" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="1">
         <v>45630</v>
       </c>
       <c r="C35" t="s">
@@ -1725,10 +1733,10 @@
       <c r="F35" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1736,7 +1744,7 @@
       <c r="A36" t="s">
         <v>79</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="1">
         <v>45631</v>
       </c>
       <c r="C36" t="s">
@@ -1748,13 +1756,13 @@
       <c r="E36" t="s">
         <v>11</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1762,7 +1770,7 @@
       <c r="A37" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="1">
         <v>45632</v>
       </c>
       <c r="C37" t="s">
@@ -1774,13 +1782,13 @@
       <c r="E37" t="s">
         <v>11</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1788,7 +1796,7 @@
       <c r="A38" t="s">
         <v>81</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38" s="1">
         <v>45633</v>
       </c>
       <c r="C38" t="s">
@@ -1800,13 +1808,13 @@
       <c r="E38" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1819,16 +1827,16 @@
     <row r="45" ht="12.75"/>
     <row r="46" ht="12.75"/>
     <row r="47" ht="12.75">
-      <c r="B47" s="4"/>
+      <c r="B47" s="1"/>
     </row>
     <row r="48" ht="12.75">
-      <c r="B48" s="4"/>
+      <c r="B48" s="1"/>
     </row>
     <row r="49" ht="12.75">
-      <c r="B49" s="4"/>
+      <c r="B49" s="1"/>
     </row>
     <row r="50" ht="12.75">
-      <c r="B50" s="4"/>
+      <c r="B50" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/crimenMeridaNOV2024.xlsx
+++ b/crimenMeridaNOV2024.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr hidePivotFieldList="0"/>
+  <workbookPr date1904="0"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
-    <sheet name="delitosNoviembre-2024" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="delitosNoviembre-2024" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
     <t>codigo</t>
   </si>
@@ -69,9 +70,6 @@
     <t>medio</t>
   </si>
   <si>
-    <t>0.5</t>
-  </si>
-  <si>
     <t>c003</t>
   </si>
   <si>
@@ -121,9 +119,6 @@
   </si>
   <si>
     <t>1.0</t>
-  </si>
-  <si>
-    <t>0.25</t>
   </si>
   <si>
     <t>c008</t>
@@ -268,8 +263,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="0\ %"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -284,7 +280,7 @@
     <font>
       <b/>
       <sz val="10.000000"/>
-      <color theme="0" tint="0"/>
+      <color theme="0"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -297,8 +293,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0"/>
-        <bgColor theme="1" tint="0"/>
+        <fgColor theme="1"/>
+        <bgColor indexed="58"/>
       </patternFill>
     </fill>
   </fills>
@@ -312,36 +308,81 @@
     </border>
   </borders>
   <cellStyleXfs count="12">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyProtection="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="13">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="9" xfId="5" applyNumberFormat="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
       <protection hidden="0" locked="1"/>
     </xf>
   </cellXfs>
@@ -350,7 +391,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
     <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
     <cellStyle name="Campo de la tabla dinámica" xfId="6"/>
     <cellStyle name="Categoría de la tabla dinámica" xfId="7"/>
@@ -653,9 +694,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="">
+    <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
@@ -663,46 +704,46 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="">
@@ -710,71 +751,25 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="25400">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -785,13 +780,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -799,10 +788,10 @@
           <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:solidFill>
-          <a:srgbClr val="000000"/>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:solidFill>
-          <a:srgbClr val="000000"/>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -813,60 +802,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="7.57421875"/>
-    <col customWidth="1" min="2" max="2" style="1" width="11.421875"/>
-    <col customWidth="1" min="3" max="3" width="25.28125"/>
-    <col customWidth="1" min="4" max="4" width="20.28125"/>
-    <col customWidth="1" min="5" max="5" width="14.421875"/>
-    <col customWidth="1" min="6" max="6" width="10.421875"/>
-    <col customWidth="1" min="7" max="7" width="7.140625"/>
-    <col customWidth="1" min="8" max="8" width="6.28125"/>
-    <col customWidth="1" min="9" max="257" width="11.5"/>
+    <col customWidth="1" min="1" max="1" style="1" width="7.5700000000000003"/>
+    <col customWidth="1" min="2" max="2" style="2" width="11.43"/>
+    <col customWidth="1" min="3" max="3" style="1" width="25.280000000000001"/>
+    <col customWidth="1" min="4" max="4" style="1" width="20.280000000000001"/>
+    <col customWidth="1" min="5" max="5" style="0" width="14.42"/>
+    <col customWidth="1" min="6" max="6" style="0" width="10.42"/>
+    <col customWidth="1" min="7" max="7" style="3" width="7.1500000000000004"/>
+    <col customWidth="1" min="8" max="8" style="0" width="11.69"/>
+    <col customWidth="1" min="9" max="257" style="0" width="11.5"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>45597</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
@@ -875,24 +864,24 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="11.25" customHeight="1">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>45598</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="s">
@@ -901,24 +890,24 @@
       <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" ht="10.5" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" ht="10.5" customHeight="1">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>45599</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="s">
@@ -927,24 +916,24 @@
       <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" ht="12.75" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>45600</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
@@ -953,103 +942,103 @@
       <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>17</v>
+      <c r="H5" s="8">
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45601</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1">
-        <v>45601</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
       <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="12.75" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" t="s">
+      <c r="B7" s="2">
+        <v>45602</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1">
-        <v>45602</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" t="s">
+      <c r="B8" s="2">
+        <v>45603</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="1">
-        <v>45603</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="8">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="9" ht="12.75">
+      <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="B9" s="2">
+        <v>45604</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="12.75">
-      <c r="A9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="1">
-        <v>45604</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -1057,155 +1046,155 @@
       <c r="F9" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="12.75">
+      <c r="A10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="2">
+        <v>45605</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="12.75">
+      <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="12.75">
-      <c r="A10" t="s">
+      <c r="B11" s="2">
+        <v>45606</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="1">
-        <v>45605</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="H11" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="12.75">
+      <c r="A12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45607</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="12.75">
+      <c r="A13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2">
+        <v>45608</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="12.75">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="1">
-        <v>45606</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="12.75">
-      <c r="A12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="1">
-        <v>45607</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="H13" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="12.75">
+      <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="2">
+        <v>45609</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="12.75">
-      <c r="A13" t="s">
+      <c r="D14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="1">
-        <v>45608</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="12.75">
-      <c r="A14" t="s">
+      <c r="H14" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="12.75">
+      <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="1">
-        <v>45609</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="12.75">
-      <c r="A15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2">
         <v>45610</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D15" t="s">
-        <v>32</v>
+      <c r="D15" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
@@ -1213,609 +1202,609 @@
       <c r="F15" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>17</v>
+      <c r="H15" s="9">
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" ht="12.75">
-      <c r="A16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="1">
+      <c r="A16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="2">
         <v>45611</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>32</v>
+      <c r="D16" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>17</v>
+      <c r="G16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0.5</v>
       </c>
     </row>
     <row r="17" ht="12.75">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="2">
+        <v>45612</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="12.75">
+      <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="1">
-        <v>45612</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B18" s="2">
+        <v>45613</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="12.75">
-      <c r="A18" t="s">
+      <c r="H18" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="12.75">
+      <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="1">
-        <v>45613</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" s="2">
+        <v>45614</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="D19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="12.75">
-      <c r="A19" t="s">
+      <c r="H19" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="12.75">
+      <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="1">
-        <v>45614</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="B20" s="2">
+        <v>45615</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D19" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="D20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H19" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="12.75">
-      <c r="A20" t="s">
+      <c r="H20" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="12.75">
+      <c r="A21" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="1">
-        <v>45615</v>
-      </c>
-      <c r="C20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="12.75">
-      <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="1">
+      <c r="B21" s="2">
         <v>45616</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D21" t="s">
-        <v>32</v>
       </c>
       <c r="E21" t="s">
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>35</v>
+      <c r="H21" s="9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="22" ht="12.75">
-      <c r="A22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="1">
+      <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="2">
         <v>45617</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
       </c>
       <c r="F22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>35</v>
+      <c r="H22" s="9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="23" ht="12.75">
-      <c r="A23" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="1">
+      <c r="A23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="2">
         <v>45618</v>
       </c>
-      <c r="C23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" t="s">
-        <v>60</v>
+      <c r="C23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="E23" t="s">
         <v>11</v>
       </c>
       <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>35</v>
+      <c r="H23" s="11">
+        <v>0.25</v>
       </c>
     </row>
     <row r="24" ht="12.75">
-      <c r="A24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="1">
+      <c r="A24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="2">
         <v>45619</v>
       </c>
-      <c r="C24" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" t="s">
-        <v>60</v>
+      <c r="C24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="E24" t="s">
         <v>11</v>
       </c>
       <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>35</v>
+      <c r="H24" s="11">
+        <v>0.25</v>
       </c>
     </row>
     <row r="25" ht="12.75">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="2">
+        <v>45620</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="12.75">
+      <c r="A26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="1">
-        <v>45620</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B26" s="2">
+        <v>45621</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="12.75">
+      <c r="A27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="2">
+        <v>45622</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H27" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="12.75">
+      <c r="A28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="2">
+        <v>45623</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E25" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" ht="12.75">
-      <c r="A26" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="1">
-        <v>45621</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="H28" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="12.75">
+      <c r="A29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="2">
+        <v>45624</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="12.75">
+      <c r="A30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="2">
+        <v>45625</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E26" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H30" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="12.75">
+      <c r="A31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="2">
+        <v>45626</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" t="s">
+        <v>69</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="12.75">
+      <c r="A32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="2">
+        <v>45627</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" ht="12.75">
-      <c r="A27" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="1">
-        <v>45622</v>
-      </c>
-      <c r="C27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" ht="12.75">
-      <c r="A28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="1">
-        <v>45623</v>
-      </c>
-      <c r="C28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" t="s">
-        <v>24</v>
-      </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H28" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" ht="12.75">
-      <c r="A29" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" s="1">
-        <v>45624</v>
-      </c>
-      <c r="C29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H29" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" ht="12.75">
-      <c r="A30" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" s="1">
-        <v>45625</v>
-      </c>
-      <c r="C30" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H30" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" ht="12.75">
-      <c r="A31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="1">
-        <v>45626</v>
-      </c>
-      <c r="C31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" t="s">
-        <v>71</v>
-      </c>
-      <c r="F31" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="3" t="s">
+      <c r="H32" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="12.75">
+      <c r="A33" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H31" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" ht="12.75">
-      <c r="A32" t="s">
+      <c r="B33" s="2">
+        <v>45628</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="12.75">
+      <c r="A34" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="1">
-        <v>45627</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B34" s="2">
+        <v>45629</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D32" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" ht="12.75">
-      <c r="A33" t="s">
+      <c r="D34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B33" s="1">
-        <v>45628</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="H34" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="12.75">
+      <c r="A35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="2">
+        <v>45630</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D33" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" ht="12.75">
-      <c r="A34" t="s">
-        <v>75</v>
-      </c>
-      <c r="B34" s="1">
-        <v>45629</v>
-      </c>
-      <c r="C34" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="3" t="s">
+      <c r="D35" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H34" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" ht="12.75">
-      <c r="A35" t="s">
+      <c r="H35" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" ht="12.75">
+      <c r="A36" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="1">
-        <v>45630</v>
-      </c>
-      <c r="C35" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" ht="12.75">
-      <c r="A36" t="s">
-        <v>79</v>
-      </c>
-      <c r="B36" s="1">
+      <c r="B36" s="2">
         <v>45631</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D36" t="s">
-        <v>32</v>
       </c>
       <c r="E36" t="s">
         <v>11</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>35</v>
+      <c r="H36" s="9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="37" ht="12.75">
-      <c r="A37" t="s">
-        <v>80</v>
-      </c>
-      <c r="B37" s="1">
+      <c r="A37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="2">
         <v>45632</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D37" t="s">
-        <v>32</v>
       </c>
       <c r="E37" t="s">
         <v>11</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G37" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>35</v>
+      <c r="H37" s="9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="38" ht="12.75">
-      <c r="A38" t="s">
-        <v>81</v>
-      </c>
-      <c r="B38" s="1">
+      <c r="A38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38" s="2">
         <v>45633</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D38" t="s">
-        <v>32</v>
       </c>
       <c r="E38" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G38" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>35</v>
+      <c r="H38" s="9">
+        <v>0.25</v>
       </c>
     </row>
     <row r="39" ht="12.75"/>
@@ -1826,21 +1815,13 @@
     <row r="44" ht="12.75"/>
     <row r="45" ht="12.75"/>
     <row r="46" ht="12.75"/>
-    <row r="47" ht="12.75">
-      <c r="B47" s="1"/>
-    </row>
-    <row r="48" ht="12.75">
-      <c r="B48" s="1"/>
-    </row>
-    <row r="49" ht="12.75">
-      <c r="B49" s="1"/>
-    </row>
-    <row r="50" ht="12.75">
-      <c r="B50" s="1"/>
-    </row>
+    <row r="47" ht="12.75"/>
+    <row r="48" ht="12.75"/>
+    <row r="49" ht="12.75"/>
+    <row r="50" ht="12.75"/>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.052778" bottom="1.052778" header="0.78750000000000009" footer="0.78750000000000009"/>
+  <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.05277777777778" bottom="1.05277777777778" header="0.78750000000000009" footer="0.78750000000000009"/>
   <pageSetup paperSize="9" scale="90" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>

--- a/crimenMeridaNOV2024.xlsx
+++ b/crimenMeridaNOV2024.xlsx
@@ -19,28 +19,28 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <si>
-    <t>codigo</t>
-  </si>
-  <si>
-    <t>fecha</t>
-  </si>
-  <si>
-    <t>descripcion</t>
-  </si>
-  <si>
-    <t>ubicación</t>
-  </si>
-  <si>
-    <t>estado</t>
-  </si>
-  <si>
-    <t>impacto</t>
-  </si>
-  <si>
-    <t>conteo</t>
-  </si>
-  <si>
-    <t>alerta</t>
+    <t>Codigo</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Ubicación</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Impacto</t>
+  </si>
+  <si>
+    <t>Conteo</t>
+  </si>
+  <si>
+    <t>Alerta</t>
   </si>
   <si>
     <t>c001</t>
